--- a/AAII_Financials/Quarterly/PMAX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PMAX_QTR_FIN.xlsx
@@ -990,10 +990,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E14" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1100,10 +1100,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E17" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="F17" s="3">
         <v>2800</v>
@@ -1147,10 +1147,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E18" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F18" s="3">
         <v>-1300</v>
@@ -1260,10 +1260,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E21" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F21" s="3">
         <v>-1200</v>
@@ -2102,10 +2102,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
         <v>100</v>
@@ -2149,10 +2149,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="E43" s="3">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="F43" s="3">
         <v>1600</v>
@@ -2751,10 +2751,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="E57" s="3">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="F57" s="3">
         <v>1200</v>
